--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486841_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486841_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1797</v>
+        <v>4.2417</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4547</v>
+        <v>3.765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.725</v>
+        <v>0.4767</v>
       </c>
       <c r="G2" t="n">
         <v>3.7979</v>
@@ -610,13 +610,13 @@
         <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8549</v>
+        <v>-0.793</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1592</v>
+        <v>-0.8489</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3043</v>
+        <v>0.056</v>
       </c>
       <c r="V2" t="n">
         <v>-0.694</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>P. DIOP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4117</v>
+        <v>3.1388</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4871</v>
+        <v>2.1834</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9246</v>
+        <v>0.9554</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6361</v>
+        <v>3.7511</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0964</v>
+        <v>1.6487</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7325</v>
+        <v>2.1024</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2713</v>
+        <v>5.3187</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9923999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2637</v>
+        <v>4.3586</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3648</v>
+        <v>-1.5676</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8961</v>
+        <v>0.6887</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5313</v>
+        <v>-2.2563</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1585</v>
+        <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9027</v>
+        <v>-1.6826</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9302</v>
+        <v>-1.4902</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0275</v>
+        <v>-0.1925</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2856</v>
+        <v>0.4911</v>
       </c>
       <c r="W3" t="n">
         <v>0.2856</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5712</v>
+        <v>0.2055</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. DIOP</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1291</v>
+        <v>2.2328</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7697</v>
+        <v>0.9358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3594</v>
+        <v>1.2971</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7511</v>
+        <v>0.6361</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6487</v>
+        <v>-0.0964</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1024</v>
+        <v>0.7325</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3187</v>
+        <v>0.2713</v>
       </c>
       <c r="K4" t="n">
-        <v>0.96</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3586</v>
+        <v>1.2637</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5676</v>
+        <v>0.3648</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6887</v>
+        <v>0.8961</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2563</v>
+        <v>-0.5313</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.51</v>
+        <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.6923</v>
+        <v>0.7239</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.9038</v>
+        <v>0.3789</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7885</v>
+        <v>0.345</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4911</v>
+        <v>-0.2856</v>
       </c>
       <c r="W4" t="n">
         <v>0.2856</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2055</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9908</v>
+        <v>1.1468</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2879</v>
+        <v>0.6674</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7028</v>
+        <v>0.4793</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2573</v>
@@ -844,13 +844,13 @@
         <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1475</v>
+        <v>0.3035</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8823</v>
+        <v>0.2618</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2652</v>
+        <v>0.0417</v>
       </c>
       <c r="V5" t="n">
         <v>0.3282</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3503</v>
+        <v>0.5034</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0414</v>
+        <v>0.1448</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3089</v>
+        <v>0.3586</v>
       </c>
       <c r="G6" t="n">
         <v>0.3172</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0331</v>
+        <v>0.1862</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9021</v>
+        <v>-1.1296</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6808</v>
+        <v>-1.7842</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.6546</v>
       </c>
       <c r="G7" t="n">
         <v>-1.491</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3034</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0279</v>
+        <v>-0.1313</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3313</v>
+        <v>0.2071</v>
       </c>
       <c r="V7" t="n">
         <v>0.2856</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9498</v>
+        <v>-1.5332</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6084</v>
+        <v>-1.9186</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6586</v>
+        <v>0.3854</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5538999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7007</v>
+        <v>0.1173</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0004</v>
+        <v>-0.3106</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.4279</v>
       </c>
       <c r="V8" t="n">
         <v>-2.255</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8217</v>
+        <v>-2.2923</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1677</v>
+        <v>-2.3403</v>
       </c>
       <c r="F9" t="n">
-        <v>0.346</v>
+        <v>0.048</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1349</v>
@@ -1156,13 +1156,13 @@
         <v>2.3169</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3017</v>
+        <v>-0.7723</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.8487</v>
+        <v>-1.0213</v>
       </c>
       <c r="U9" t="n">
-        <v>0.547</v>
+        <v>0.249</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7366</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9928</v>
+        <v>-2.6329</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6576</v>
+        <v>-3.3473</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.7145</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1691</v>
@@ -1234,13 +1234,13 @@
         <v>2.7031</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3461</v>
+        <v>-0.9862</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.966</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3801</v>
+        <v>-0.3304</v>
       </c>
       <c r="V10" t="n">
         <v>0.8193</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2715</v>
+        <v>-4.5516</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9209</v>
+        <v>-4.3004</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3505</v>
+        <v>-0.2512</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8606</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6163</v>
+        <v>-0.8964</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4624</v>
+        <v>-0.8419</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1539</v>
+        <v>-0.0546</v>
       </c>
       <c r="V11" t="n">
         <v>0.2055</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8762999999999979</v>
+        <v>-0.8760999999999997</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9946</v>
+        <v>-5.994400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1183</v>
+        <v>5.1184</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.9645</v>
+        <v>-4.964500000000001</v>
       </c>
       <c r="H12" t="n">
         <v>2.416700000000001</v>
@@ -1363,7 +1363,7 @@
         <v>-7.381200000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.806300000000002</v>
+        <v>1.8063</v>
       </c>
       <c r="K12" t="n">
         <v>0.008600000000000052</v>
@@ -1390,10 +1390,10 @@
         <v>16.4117</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7239</v>
+        <v>-3.7238</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.5559</v>
+        <v>-4.555800000000001</v>
       </c>
       <c r="U12" t="n">
         <v>0.8320000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.333600000000001</v>
+        <v>8.8551</v>
       </c>
       <c r="E13" t="n">
         <v>7.4776</v>
       </c>
       <c r="F13" t="n">
-        <v>0.856</v>
+        <v>1.3775</v>
       </c>
       <c r="G13" t="n">
         <v>8.995200000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0664</v>
+        <v>0.4551</v>
       </c>
       <c r="T13" t="n">
         <v>-0.1386</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0722</v>
+        <v>0.5937</v>
       </c>
       <c r="V13" t="n">
         <v>1.1424</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5544</v>
+        <v>3.3572</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0384</v>
+        <v>2.7281</v>
       </c>
       <c r="F14" t="n">
-        <v>0.516</v>
+        <v>0.6291</v>
       </c>
       <c r="G14" t="n">
         <v>2.0593</v>
@@ -1546,13 +1546,13 @@
         <v>0.7723</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1971</v>
+        <v>0.9999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3857</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8114</v>
+        <v>0.9245</v>
       </c>
       <c r="V14" t="n">
         <v>0.4911</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.08</v>
+        <v>2.6275</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8961</v>
+        <v>1.2064</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1839</v>
+        <v>1.4211</v>
       </c>
       <c r="G15" t="n">
         <v>1.6054</v>
@@ -1624,13 +1624,13 @@
         <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5681</v>
+        <v>-0.0206</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6347</v>
+        <v>-0.3244</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3038</v>
       </c>
       <c r="V15" t="n">
         <v>0.6565</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8619</v>
+        <v>1.0179</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9053</v>
+        <v>0.2848</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9566</v>
+        <v>0.7331</v>
       </c>
       <c r="G16" t="n">
         <v>2.7324</v>
@@ -1702,13 +1702,13 @@
         <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5612</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6064000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9548</v>
+        <v>0.7313</v>
       </c>
       <c r="V16" t="n">
         <v>-0.694</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5492</v>
+        <v>-0.3961</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3836</v>
+        <v>-0.334</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1311</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1324</v>
+        <v>0.0206</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9395</v>
+        <v>-1.3232</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2776</v>
+        <v>-1.2963</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3382</v>
+        <v>-0.0269</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1023</v>
+        <v>-1.1412</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.9508</v>
+        <v>-0.931</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1515</v>
+        <v>-0.2102</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.2386</v>
+        <v>-1.2989</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.6049</v>
+        <v>-1.3442</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3662</v>
+        <v>0.0453</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8637</v>
+        <v>0.1577</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3459</v>
+        <v>0.4132</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5178</v>
+        <v>-0.2555</v>
       </c>
       <c r="P18" t="n">
         <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9352</v>
+        <v>0.4275</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9923</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>1.9428</v>
+        <v>0.3589</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1628</v>
       </c>
       <c r="W18" t="n">
         <v>0.8995</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8995</v>
+        <v>-0.7366</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7982</v>
+        <v>-1.6988</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8985</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.8003</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8367</v>
@@ -1936,13 +1936,13 @@
         <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5407</v>
+        <v>-0.4413</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3311</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2096</v>
+        <v>-0.1102</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6138</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8281</v>
+        <v>-1.7657</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5031</v>
+        <v>-1.5648</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3249</v>
+        <v>-0.2009</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1412</v>
+        <v>-1.1519</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.931</v>
+        <v>-1.4142</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2102</v>
+        <v>0.2623</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2989</v>
+        <v>0.0009</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3442</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0453</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1577</v>
+        <v>-1.1528</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4132</v>
+        <v>-0.7594</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2555</v>
+        <v>-0.3934</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7723</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0774</v>
+        <v>-0.4207</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1383</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0609</v>
+        <v>0.1796</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1628</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3491</v>
+        <v>-2.5436</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.875</v>
+        <v>-3.0016</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4741</v>
+        <v>0.458</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1519</v>
+        <v>-3.1023</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4142</v>
+        <v>-2.9508</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2623</v>
+        <v>-0.1515</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0009</v>
+        <v>-2.2386</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-2.6049</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.3662</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1528</v>
+        <v>-0.8637</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7594</v>
+        <v>-0.3459</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3934</v>
+        <v>-0.5178</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0041</v>
+        <v>1.331</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9106</v>
+        <v>0.2684</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0936</v>
+        <v>1.0626</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6016</v>
+        <v>-3.112</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0703</v>
+        <v>-3.9669</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4687</v>
+        <v>0.8549</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6789</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2207</v>
+        <v>0.2689</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0269</v>
+        <v>0.1304</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2477</v>
+        <v>0.1385</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8881</v>
+        <v>-3.4525</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.6456</v>
+        <v>-6.0251</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7575</v>
+        <v>2.5726</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3856</v>
@@ -2248,13 +2248,13 @@
         <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6403</v>
+        <v>1.0759</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5245</v>
+        <v>0.096</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1648</v>
+        <v>0.9799</v>
       </c>
       <c r="V23" t="n">
         <v>1.1049</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8761000000000005</v>
+        <v>1.565800000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.118200000000001</v>
+        <v>-5.1184</v>
       </c>
       <c r="F24" t="n">
-        <v>5.9946</v>
+        <v>6.684200000000001</v>
       </c>
       <c r="G24" t="n">
         <v>4.964600000000001</v>
@@ -2299,7 +2299,7 @@
         <v>7.3815</v>
       </c>
       <c r="J24" t="n">
-        <v>6.770999999999996</v>
+        <v>6.771</v>
       </c>
       <c r="K24" t="n">
         <v>-2.4081</v>
@@ -2311,7 +2311,7 @@
         <v>-1.8064</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.008399999999999963</v>
+        <v>-0.008399999999999852</v>
       </c>
       <c r="O24" t="n">
         <v>-1.7979</v>
@@ -2326,13 +2326,13 @@
         <v>6.7578</v>
       </c>
       <c r="S24" t="n">
-        <v>3.724</v>
+        <v>4.4135</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8320000000000001</v>
+        <v>-0.8318000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5557</v>
+        <v>5.245399999999999</v>
       </c>
       <c r="V24" t="n">
         <v>1.8415</v>
